--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>22.36070833590424</v>
+      </c>
+      <c r="C2">
         <v>34.18961628377313</v>
-      </c>
-      <c r="C2">
-        <v>22.36070833590424</v>
       </c>
       <c r="D2">
         <v>2.924864648085021</v>
       </c>
       <c r="E2">
-        <v>21.83937744417536</v>
+        <v>14.28339953317072</v>
       </c>
       <c r="F2">
         <v>63.87722302265393</v>
       </c>
       <c r="G2">
-        <v>14.28339953317072</v>
+        <v>21.83937744417536</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.54762788435696</v>
+      </c>
+      <c r="C3">
         <v>30.52075201249088</v>
-      </c>
-      <c r="C3">
-        <v>30.54762788435696</v>
       </c>
       <c r="D3">
         <v>3.276459241865146</v>
       </c>
       <c r="E3">
-        <v>18.94894083620703</v>
+        <v>18.96562683744657</v>
       </c>
       <c r="F3">
         <v>62.08543232634641</v>
       </c>
       <c r="G3">
-        <v>18.96562683744657</v>
+        <v>18.94894083620703</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.94159801872376</v>
+      </c>
+      <c r="C4">
         <v>35.04997101856569</v>
-      </c>
-      <c r="C4">
-        <v>24.94159801872376</v>
       </c>
       <c r="D4">
         <v>2.853069406163869</v>
       </c>
       <c r="E4">
-        <v>21.90738626383278</v>
+        <v>15.58932021781135</v>
       </c>
       <c r="F4">
         <v>62.50329351835587</v>
       </c>
       <c r="G4">
-        <v>15.58932021781135</v>
+        <v>21.90738626383278</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.97514521140078</v>
+      </c>
+      <c r="C5">
         <v>46.77833310819938</v>
-      </c>
-      <c r="C5">
-        <v>27.97514521140078</v>
       </c>
       <c r="D5">
         <v>2.137741842333237</v>
       </c>
       <c r="E5">
-        <v>26.76818427765324</v>
+        <v>16.00834814872072</v>
       </c>
       <c r="F5">
         <v>57.22346757362603</v>
       </c>
       <c r="G5">
-        <v>16.00834814872072</v>
+        <v>26.76818427765324</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.41438106455774</v>
+      </c>
+      <c r="C6">
         <v>31.57215772056761</v>
-      </c>
-      <c r="C6">
-        <v>28.41438106455774</v>
       </c>
       <c r="D6">
         <v>3.167347663883461</v>
       </c>
       <c r="E6">
-        <v>19.73425886972374</v>
+        <v>17.7604824007853</v>
       </c>
       <c r="F6">
         <v>62.50525872949095</v>
       </c>
       <c r="G6">
-        <v>17.7604824007853</v>
+        <v>19.73425886972374</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.94163643408122</v>
+      </c>
+      <c r="C7">
         <v>39.61114437673911</v>
-      </c>
-      <c r="C7">
-        <v>26.94163643408122</v>
       </c>
       <c r="D7">
         <v>2.524542059398897</v>
       </c>
       <c r="E7">
+        <v>16.1760351901197</v>
+      </c>
+      <c r="F7">
+        <v>60.0410269424354</v>
+      </c>
+      <c r="G7">
         <v>23.78293786744491</v>
-      </c>
-      <c r="F7">
-        <v>60.04102694243539</v>
-      </c>
-      <c r="G7">
-        <v>16.17603519011969</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.73626232042775</v>
+      </c>
+      <c r="C8">
         <v>36.8324421825678</v>
-      </c>
-      <c r="C8">
-        <v>27.73626232042775</v>
       </c>
       <c r="D8">
         <v>2.714997813729777</v>
       </c>
       <c r="E8">
-        <v>22.38119470758631</v>
+        <v>16.85391059265638</v>
       </c>
       <c r="F8">
         <v>60.7648946997573</v>
       </c>
       <c r="G8">
-        <v>16.85391059265638</v>
+        <v>22.38119470758631</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.59195661997289</v>
+      </c>
+      <c r="C9">
         <v>25.51739719837325</v>
-      </c>
-      <c r="C9">
-        <v>30.59195661997289</v>
       </c>
       <c r="D9">
         <v>3.918894988489463</v>
       </c>
       <c r="E9">
-        <v>16.34584768576143</v>
+        <v>19.59649173589603</v>
       </c>
       <c r="F9">
         <v>64.05766057834255</v>
       </c>
       <c r="G9">
-        <v>19.59649173589603</v>
+        <v>16.34584768576143</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.07374354156881</v>
+      </c>
+      <c r="C10">
         <v>37.82996712071395</v>
-      </c>
-      <c r="C10">
-        <v>27.07374354156881</v>
       </c>
       <c r="D10">
         <v>2.643407002731562</v>
       </c>
       <c r="E10">
+        <v>16.41791044776119</v>
+      </c>
+      <c r="F10">
+        <v>60.64144924233792</v>
+      </c>
+      <c r="G10">
         <v>22.94064030990087</v>
-      </c>
-      <c r="F10">
-        <v>60.64144924233793</v>
-      </c>
-      <c r="G10">
-        <v>16.4179104477612</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.35040947900331</v>
+      </c>
+      <c r="C11">
         <v>40.43387349712494</v>
-      </c>
-      <c r="C11">
-        <v>26.35040947900331</v>
       </c>
       <c r="D11">
         <v>2.473173884938591</v>
       </c>
       <c r="E11">
-        <v>24.24321571290517</v>
+        <v>15.79909629900489</v>
       </c>
       <c r="F11">
         <v>59.95768798808996</v>
       </c>
       <c r="G11">
-        <v>15.79909629900489</v>
+        <v>24.24321571290517</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>26.39027362357372</v>
+      </c>
+      <c r="C12">
         <v>40.51179793951479</v>
-      </c>
-      <c r="C12">
-        <v>26.39027362357372</v>
       </c>
       <c r="D12">
         <v>2.468416735028712</v>
       </c>
       <c r="E12">
+        <v>15.81183107939932</v>
+      </c>
+      <c r="F12">
+        <v>59.91537376586742</v>
+      </c>
+      <c r="G12">
         <v>24.27279515473326</v>
-      </c>
-      <c r="F12">
-        <v>59.91537376586741</v>
-      </c>
-      <c r="G12">
-        <v>15.81183107939932</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>24.11394000504159</v>
+      </c>
+      <c r="C13">
         <v>35.83060247038064</v>
-      </c>
-      <c r="C13">
-        <v>24.11394000504159</v>
       </c>
       <c r="D13">
         <v>2.79091037005769</v>
       </c>
       <c r="E13">
-        <v>22.40189125295508</v>
+        <v>15.07643814026793</v>
       </c>
       <c r="F13">
-        <v>62.52167060677698</v>
+        <v>62.52167060677699</v>
       </c>
       <c r="G13">
-        <v>15.07643814026792</v>
+        <v>22.40189125295509</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>29.62615176947004</v>
+      </c>
+      <c r="C14">
         <v>31.88567404190387</v>
-      </c>
-      <c r="C14">
-        <v>29.62615176947004</v>
       </c>
       <c r="D14">
         <v>3.136204675133444</v>
       </c>
       <c r="E14">
-        <v>19.74200581395349</v>
+        <v>18.34302325581396</v>
       </c>
       <c r="F14">
         <v>61.91497093023257</v>
       </c>
       <c r="G14">
-        <v>18.34302325581396</v>
+        <v>19.74200581395349</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.32727272727273</v>
+      </c>
+      <c r="C15">
         <v>31.41010101010101</v>
-      </c>
-      <c r="C15">
-        <v>28.32727272727273</v>
       </c>
       <c r="D15">
         <v>3.183689220478518</v>
       </c>
       <c r="E15">
-        <v>19.66358922473757</v>
+        <v>17.73365372454787</v>
       </c>
       <c r="F15">
         <v>62.60275705071456</v>
       </c>
       <c r="G15">
-        <v>17.73365372454787</v>
+        <v>19.66358922473757</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>31.79620343839542</v>
+      </c>
+      <c r="C16">
         <v>33.376611747851</v>
-      </c>
-      <c r="C16">
-        <v>31.79620343839542</v>
       </c>
       <c r="D16">
         <v>2.996109993293092</v>
       </c>
       <c r="E16">
-        <v>20.20708535494538</v>
+        <v>19.25026427777627</v>
       </c>
       <c r="F16">
         <v>60.54265036727834</v>
       </c>
       <c r="G16">
-        <v>19.25026427777627</v>
+        <v>20.20708535494538</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.01289134438305</v>
+      </c>
+      <c r="C17">
         <v>36.69429097605893</v>
-      </c>
-      <c r="C17">
-        <v>26.01289134438305</v>
       </c>
       <c r="D17">
         <v>2.725219573400251</v>
       </c>
       <c r="E17">
-        <v>22.55234861346915</v>
+        <v>15.98754951895869</v>
       </c>
       <c r="F17">
-        <v>61.46010186757215</v>
+        <v>61.46010186757216</v>
       </c>
       <c r="G17">
-        <v>15.98754951895868</v>
+        <v>22.55234861346916</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.86760082637205</v>
+      </c>
+      <c r="C18">
         <v>33.51747058295159</v>
-      </c>
-      <c r="C18">
-        <v>27.86760082637205</v>
       </c>
       <c r="D18">
         <v>2.983518692214927</v>
       </c>
       <c r="E18">
-        <v>20.76863137975177</v>
+        <v>17.26776868703735</v>
       </c>
       <c r="F18">
         <v>61.96359993321088</v>
       </c>
       <c r="G18">
-        <v>17.26776868703735</v>
+        <v>20.76863137975177</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>31.19116354964228</v>
+      </c>
+      <c r="C19">
         <v>28.4611522530438</v>
-      </c>
-      <c r="C19">
-        <v>31.19116354964228</v>
       </c>
       <c r="D19">
         <v>3.513561190738699</v>
       </c>
       <c r="E19">
-        <v>17.82695860686347</v>
+        <v>19.53693148315579</v>
       </c>
       <c r="F19">
         <v>62.63610990998074</v>
       </c>
       <c r="G19">
-        <v>19.53693148315579</v>
+        <v>17.82695860686347</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>33.52737352737353</v>
+      </c>
+      <c r="C20">
         <v>26.37560637560637</v>
-      </c>
-      <c r="C20">
-        <v>33.52737352737353</v>
       </c>
       <c r="D20">
         <v>3.791382028376248</v>
       </c>
       <c r="E20">
-        <v>16.49475600242697</v>
+        <v>20.96732252752016</v>
       </c>
       <c r="F20">
         <v>62.53792147005288</v>
       </c>
       <c r="G20">
-        <v>20.96732252752016</v>
+        <v>16.49475600242697</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.22785309619776</v>
+      </c>
+      <c r="C21">
         <v>30.29890921390118</v>
-      </c>
-      <c r="C21">
-        <v>29.22785309619776</v>
       </c>
       <c r="D21">
         <v>3.30044884764762</v>
       </c>
       <c r="E21">
-        <v>18.99299451398889</v>
+        <v>18.32159862893893</v>
       </c>
       <c r="F21">
         <v>62.68540685707218</v>
       </c>
       <c r="G21">
-        <v>18.32159862893893</v>
+        <v>18.99299451398889</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.32902298850574</v>
+      </c>
+      <c r="C22">
         <v>44.86350574712644</v>
-      </c>
-      <c r="C22">
-        <v>26.32902298850574</v>
       </c>
       <c r="D22">
         <v>2.22898318654924</v>
       </c>
       <c r="E22">
-        <v>26.20646244229962</v>
+        <v>15.3797733948804</v>
       </c>
       <c r="F22">
         <v>58.41376416281997</v>
       </c>
       <c r="G22">
-        <v>15.3797733948804</v>
+        <v>26.20646244229962</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.80057388809182</v>
+      </c>
+      <c r="C23">
         <v>33.18507890961263</v>
-      </c>
-      <c r="C23">
-        <v>26.80057388809182</v>
       </c>
       <c r="D23">
         <v>3.013402507565932</v>
       </c>
       <c r="E23">
-        <v>20.74253430185634</v>
+        <v>16.75186081965743</v>
       </c>
       <c r="F23">
         <v>62.50560487848623</v>
       </c>
       <c r="G23">
-        <v>16.75186081965743</v>
+        <v>20.74253430185634</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.94832437963673</v>
+      </c>
+      <c r="C24">
         <v>37.25377334356612</v>
-      </c>
-      <c r="C24">
-        <v>27.94832437963673</v>
       </c>
       <c r="D24">
         <v>2.684291845493562</v>
       </c>
       <c r="E24">
-        <v>22.55042390925631</v>
+        <v>16.91765707870388</v>
       </c>
       <c r="F24">
-        <v>60.53191901203979</v>
+        <v>60.5319190120398</v>
       </c>
       <c r="G24">
-        <v>16.91765707870388</v>
+        <v>22.55042390925632</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.81951121794872</v>
+      </c>
+      <c r="C25">
         <v>35.75220352564102</v>
-      </c>
-      <c r="C25">
-        <v>27.81951121794872</v>
       </c>
       <c r="D25">
         <v>2.797030396414064</v>
       </c>
       <c r="E25">
-        <v>21.85720409038026</v>
+        <v>17.00753168820036</v>
       </c>
       <c r="F25">
         <v>61.13526422141939</v>
       </c>
       <c r="G25">
-        <v>17.00753168820036</v>
+        <v>21.85720409038026</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>28.89420831387202</v>
+      </c>
+      <c r="C26">
         <v>35.43320878094349</v>
-      </c>
-      <c r="C26">
-        <v>28.89420831387202</v>
       </c>
       <c r="D26">
         <v>2.822211237436151</v>
       </c>
       <c r="E26">
-        <v>21.56256661692603</v>
+        <v>17.58331556881973</v>
       </c>
       <c r="F26">
         <v>60.85411781425424</v>
       </c>
       <c r="G26">
-        <v>17.58331556881973</v>
+        <v>21.56256661692603</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>26.17168228909719</v>
+      </c>
+      <c r="C27">
         <v>34.38579181055748</v>
-      </c>
-      <c r="C27">
-        <v>26.17168228909719</v>
       </c>
       <c r="D27">
         <v>2.908177905308465</v>
       </c>
       <c r="E27">
-        <v>21.41650023045015</v>
+        <v>16.3005069903211</v>
       </c>
       <c r="F27">
         <v>62.28299277922876</v>
       </c>
       <c r="G27">
-        <v>16.3005069903211</v>
+        <v>21.41650023045015</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.37279218338971</v>
+      </c>
+      <c r="C28">
         <v>50.50732807215332</v>
-      </c>
-      <c r="C28">
-        <v>28.37279218338971</v>
       </c>
       <c r="D28">
         <v>1.979910714285714</v>
       </c>
       <c r="E28">
-        <v>28.23529411764706</v>
+        <v>15.86134453781513</v>
       </c>
       <c r="F28">
         <v>55.90336134453781</v>
       </c>
       <c r="G28">
-        <v>15.86134453781513</v>
+        <v>28.23529411764706</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>26.66240409207161</v>
+      </c>
+      <c r="C29">
         <v>42.56713554987212</v>
-      </c>
-      <c r="C29">
-        <v>26.66240409207161</v>
       </c>
       <c r="D29">
         <v>2.349230191513331</v>
       </c>
       <c r="E29">
-        <v>25.15349012940398</v>
+        <v>15.75517143666761</v>
       </c>
       <c r="F29">
         <v>59.0913384339284</v>
       </c>
       <c r="G29">
-        <v>15.75517143666761</v>
+        <v>25.15349012940398</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>24.7976139752876</v>
+      </c>
+      <c r="C30">
         <v>45.2066467831274</v>
-      </c>
-      <c r="C30">
-        <v>24.7976139752876</v>
       </c>
       <c r="D30">
         <v>2.212064090480679</v>
       </c>
       <c r="E30">
-        <v>26.59147869674186</v>
+        <v>14.58646616541354</v>
       </c>
       <c r="F30">
         <v>58.82205513784461</v>
       </c>
       <c r="G30">
-        <v>14.58646616541354</v>
+        <v>26.59147869674186</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>27.95576684580405</v>
+      </c>
+      <c r="C31">
         <v>36.52335675899132</v>
-      </c>
-      <c r="C31">
-        <v>27.95576684580405</v>
       </c>
       <c r="D31">
         <v>2.737973967176004</v>
       </c>
       <c r="E31">
-        <v>22.20546654099905</v>
+        <v>16.99654414074772</v>
       </c>
       <c r="F31">
         <v>60.79798931825322</v>
       </c>
       <c r="G31">
-        <v>16.99654414074772</v>
+        <v>22.20546654099905</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.76572933320794</v>
+      </c>
+      <c r="C32">
         <v>39.1516975453776</v>
-      </c>
-      <c r="C32">
-        <v>26.76572933320794</v>
       </c>
       <c r="D32">
         <v>2.554167667547442</v>
       </c>
       <c r="E32">
+        <v>16.13195782791067</v>
+      </c>
+      <c r="F32">
+        <v>60.2709443373767</v>
+      </c>
+      <c r="G32">
         <v>23.59709783471262</v>
-      </c>
-      <c r="F32">
-        <v>60.27094433737672</v>
-      </c>
-      <c r="G32">
-        <v>16.13195782791067</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>26.65688944758712</v>
+      </c>
+      <c r="C33">
         <v>45.14980096375445</v>
-      </c>
-      <c r="C33">
-        <v>26.65688944758712</v>
       </c>
       <c r="D33">
         <v>2.214849187935035</v>
       </c>
       <c r="E33">
-        <v>26.27941953579123</v>
+        <v>15.51562944595748</v>
       </c>
       <c r="F33">
         <v>58.20495101825129</v>
       </c>
       <c r="G33">
-        <v>15.51562944595748</v>
+        <v>26.27941953579123</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>36.76562175627984</v>
+      </c>
+      <c r="C34">
         <v>21.77703965123521</v>
-      </c>
-      <c r="C34">
-        <v>36.76562175627984</v>
       </c>
       <c r="D34">
         <v>4.591992373689227</v>
       </c>
       <c r="E34">
-        <v>13.73576011522849</v>
+        <v>23.1897341888176</v>
       </c>
       <c r="F34">
         <v>63.07450569595391</v>
       </c>
       <c r="G34">
-        <v>23.1897341888176</v>
+        <v>13.73576011522849</v>
       </c>
     </row>
   </sheetData>
